--- a/research/traditional_assets/database/data/singapore/singapore_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0431</v>
+        <v>0.0392</v>
       </c>
       <c r="E2">
-        <v>0.1145</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="F2">
-        <v>0.0454</v>
+        <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0.3823011889319265</v>
+        <v>0.4010827426791831</v>
       </c>
       <c r="H2">
-        <v>0.2877580223386099</v>
+        <v>0.3055399795876381</v>
       </c>
       <c r="I2">
-        <v>0.2720530970959028</v>
+        <v>0.2896496920470386</v>
       </c>
       <c r="J2">
-        <v>0.2465699438889214</v>
+        <v>0.2505526980661979</v>
       </c>
       <c r="K2">
-        <v>310.627</v>
+        <v>379.545</v>
       </c>
       <c r="L2">
-        <v>0.256486115365783</v>
+        <v>0.3062217363416691</v>
       </c>
       <c r="M2">
-        <v>343.159</v>
+        <v>321.51</v>
       </c>
       <c r="N2">
-        <v>0.03964268798447374</v>
+        <v>0.03806793761078135</v>
       </c>
       <c r="O2">
-        <v>1.104730110389631</v>
+        <v>0.8470932300517725</v>
       </c>
       <c r="P2">
-        <v>331.359</v>
+        <v>301.61</v>
       </c>
       <c r="Q2">
-        <v>0.03827951896306736</v>
+        <v>0.03571170620754491</v>
       </c>
       <c r="R2">
-        <v>1.066742427412942</v>
+        <v>0.7946620295353647</v>
       </c>
       <c r="S2">
-        <v>11.80000000000001</v>
+        <v>19.89999999999998</v>
       </c>
       <c r="T2">
-        <v>0.03438639231376712</v>
+        <v>0.06189543093527411</v>
       </c>
       <c r="U2">
-        <v>1560.49</v>
+        <v>1436.84</v>
       </c>
       <c r="V2">
-        <v>0.1802721717130876</v>
+        <v>0.1701270115289574</v>
       </c>
       <c r="W2">
-        <v>0.08225268618006669</v>
+        <v>0.03886953034288831</v>
       </c>
       <c r="X2">
-        <v>0.02329272187747412</v>
+        <v>0.05101378443741835</v>
       </c>
       <c r="Y2">
-        <v>0.05895996430259257</v>
+        <v>-0.01214425409453004</v>
       </c>
       <c r="Z2">
-        <v>0.6805430328042996</v>
+        <v>0.5292470121719213</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02315922156369462</v>
+        <v>0.04805181993338715</v>
       </c>
       <c r="AC2">
-        <v>-0.02308117462400067</v>
+        <v>-0.04760512658365952</v>
       </c>
       <c r="AD2">
-        <v>1026.987</v>
+        <v>1232.59</v>
       </c>
       <c r="AE2">
-        <v>2.170153987072248</v>
+        <v>0.005687203791469195</v>
       </c>
       <c r="AF2">
-        <v>1029.157153987072</v>
+        <v>1232.595687203791</v>
       </c>
       <c r="AG2">
-        <v>-531.3328460129278</v>
+        <v>-204.2443127962088</v>
       </c>
       <c r="AH2">
-        <v>0.1062579842773259</v>
+        <v>0.1273568198997758</v>
       </c>
       <c r="AI2">
-        <v>0.2426423553564934</v>
+        <v>0.265892278176543</v>
       </c>
       <c r="AJ2">
-        <v>-0.06539507618220869</v>
+        <v>-0.0247825831229261</v>
       </c>
       <c r="AK2">
-        <v>-0.1981870032323007</v>
+        <v>-0.06384918007187264</v>
       </c>
       <c r="AL2">
-        <v>7.18</v>
+        <v>6.991</v>
       </c>
       <c r="AM2">
-        <v>2.148</v>
+        <v>3.558</v>
       </c>
       <c r="AN2">
-        <v>2.90015927074332</v>
+        <v>3.224092742462843</v>
       </c>
       <c r="AO2">
-        <v>45.82172701949861</v>
+        <v>51.3517379487913</v>
       </c>
       <c r="AP2">
-        <v>-1.50045704494295</v>
+        <v>-0.534243022071871</v>
       </c>
       <c r="AQ2">
-        <v>153.1657355679702</v>
+        <v>100.8993816750984</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0524</v>
+        <v>0.0654</v>
       </c>
       <c r="E3">
+        <v>0.0585</v>
+      </c>
+      <c r="F3">
         <v>0.05</v>
       </c>
-      <c r="F3">
-        <v>0.0454</v>
-      </c>
       <c r="G3">
-        <v>0.6683225066870463</v>
+        <v>0.6579746835443039</v>
       </c>
       <c r="H3">
-        <v>0.5307604126862819</v>
+        <v>0.5184810126582279</v>
       </c>
       <c r="I3">
-        <v>0.5026111323398293</v>
+        <v>0.4906329113924051</v>
       </c>
       <c r="J3">
-        <v>0.4176876168730344</v>
+        <v>0.4071689218681799</v>
       </c>
       <c r="K3">
-        <v>331.2</v>
+        <v>324.5</v>
       </c>
       <c r="L3">
-        <v>0.4218570882690103</v>
+        <v>0.4107594936708861</v>
       </c>
       <c r="M3">
-        <v>266.5</v>
+        <v>265.9</v>
       </c>
       <c r="N3">
-        <v>0.03614833704085509</v>
+        <v>0.03727587512091177</v>
       </c>
       <c r="O3">
-        <v>0.8046497584541064</v>
+        <v>0.8194144838212634</v>
       </c>
       <c r="P3">
-        <v>254.7</v>
+        <v>246</v>
       </c>
       <c r="Q3">
-        <v>0.03454777277413054</v>
+        <v>0.03448614245860962</v>
       </c>
       <c r="R3">
-        <v>0.7690217391304348</v>
+        <v>0.7580893682588598</v>
       </c>
       <c r="S3">
-        <v>11.80000000000001</v>
+        <v>19.89999999999998</v>
       </c>
       <c r="T3">
-        <v>0.04427767354596627</v>
+        <v>0.07484016547574268</v>
       </c>
       <c r="U3">
-        <v>788.2</v>
+        <v>717.2</v>
       </c>
       <c r="V3">
-        <v>0.1069122673756172</v>
+        <v>0.1005425258996537</v>
       </c>
       <c r="W3">
-        <v>0.370926195542614</v>
+        <v>0.3151403321355735</v>
       </c>
       <c r="X3">
-        <v>0.02329272187747412</v>
+        <v>0.04875070882860448</v>
       </c>
       <c r="Y3">
-        <v>0.3476334736651399</v>
+        <v>0.266389623306969</v>
       </c>
       <c r="Z3">
-        <v>2.726988537686696</v>
+        <v>3.291666666666668</v>
       </c>
       <c r="AA3">
-        <v>1.139029343546437</v>
+        <v>1.340264367816093</v>
       </c>
       <c r="AB3">
-        <v>0.02309078663253827</v>
+        <v>0.04805180113594073</v>
       </c>
       <c r="AC3">
-        <v>1.115938556913899</v>
+        <v>1.292212566680152</v>
       </c>
       <c r="AD3">
-        <v>400.9</v>
+        <v>567</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>400.9</v>
+        <v>567</v>
       </c>
       <c r="AG3">
-        <v>-387.3000000000001</v>
+        <v>-150.2</v>
       </c>
       <c r="AH3">
-        <v>0.05157397758995536</v>
+        <v>0.07363349479890394</v>
       </c>
       <c r="AI3">
-        <v>0.2795286570910612</v>
+        <v>0.3373393622084722</v>
       </c>
       <c r="AJ3">
-        <v>-0.05544659346322889</v>
+        <v>-0.0215090719021638</v>
       </c>
       <c r="AK3">
-        <v>-0.5995356037151705</v>
+        <v>-0.1558738065587381</v>
       </c>
       <c r="AL3">
-        <v>3.56</v>
+        <v>5.31</v>
       </c>
       <c r="AM3">
-        <v>-0.8699999999999997</v>
+        <v>2.29</v>
       </c>
       <c r="AN3">
-        <v>0.9620830333573314</v>
+        <v>1.38427734375</v>
       </c>
       <c r="AO3">
-        <v>110.8426966292135</v>
+        <v>72.99435028248588</v>
       </c>
       <c r="AP3">
-        <v>-0.9294456443484523</v>
+        <v>-0.3666992187500001</v>
       </c>
       <c r="AQ3">
-        <v>-453.5632183908048</v>
+        <v>169.2576419213974</v>
       </c>
     </row>
     <row r="4">
@@ -862,46 +862,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0338</v>
+        <v>0.0392</v>
       </c>
       <c r="E4">
-        <v>0.269</v>
+        <v>0.224</v>
       </c>
       <c r="G4">
-        <v>0.1195698924731183</v>
+        <v>0.1689284043051006</v>
       </c>
       <c r="H4">
-        <v>0.1195698924731183</v>
+        <v>0.1689284043051006</v>
       </c>
       <c r="I4">
-        <v>0.1362371464890912</v>
+        <v>0.1806270472625176</v>
       </c>
       <c r="J4">
-        <v>0.1146694630167337</v>
+        <v>0.1542782959506795</v>
       </c>
       <c r="K4">
-        <v>29.4</v>
+        <v>34.7</v>
       </c>
       <c r="L4">
-        <v>0.1264516129032258</v>
+        <v>0.1623771642489471</v>
       </c>
       <c r="M4">
-        <v>8.68</v>
+        <v>1.28</v>
       </c>
       <c r="N4">
-        <v>0.04719956498096792</v>
+        <v>0.006823027718550107</v>
       </c>
       <c r="O4">
-        <v>0.2952380952380952</v>
+        <v>0.03688760806916426</v>
       </c>
       <c r="P4">
-        <v>8.68</v>
+        <v>1.28</v>
       </c>
       <c r="Q4">
-        <v>0.04719956498096792</v>
+        <v>0.006823027718550107</v>
       </c>
       <c r="R4">
-        <v>0.2952380952380952</v>
+        <v>0.03688760806916426</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,73 +910,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>15.7</v>
+        <v>34.3</v>
       </c>
       <c r="V4">
-        <v>0.08537248504622076</v>
+        <v>0.1828358208955224</v>
       </c>
       <c r="W4">
-        <v>0.1857233101705622</v>
+        <v>0.1559550561797753</v>
       </c>
       <c r="X4">
-        <v>0.03236277365685661</v>
+        <v>0.06404371481419231</v>
       </c>
       <c r="Y4">
-        <v>0.1533605365137056</v>
+        <v>0.09191134136558297</v>
       </c>
       <c r="Z4">
-        <v>0.6260698436214039</v>
+        <v>0.4558447098976109</v>
       </c>
       <c r="AA4">
-        <v>0.07179109277903684</v>
+        <v>0.07032694506113524</v>
       </c>
       <c r="AB4">
-        <v>0.02468089938728863</v>
+        <v>0.04737634025688282</v>
       </c>
       <c r="AC4">
-        <v>0.0471101933917482</v>
+        <v>0.02295060480425242</v>
       </c>
       <c r="AD4">
-        <v>264.2</v>
+        <v>385.2</v>
       </c>
       <c r="AE4">
-        <v>2.1643172064314</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>266.3643172064314</v>
+        <v>385.2</v>
       </c>
       <c r="AG4">
-        <v>250.6643172064314</v>
+        <v>350.9</v>
       </c>
       <c r="AH4">
-        <v>0.5915732316054529</v>
+        <v>0.6724860335195532</v>
       </c>
       <c r="AI4">
-        <v>0.5408804412823613</v>
+        <v>0.6046146601789357</v>
       </c>
       <c r="AJ4">
-        <v>0.5768175325986513</v>
+        <v>0.6516248839368616</v>
       </c>
       <c r="AK4">
-        <v>0.5257614887690887</v>
+        <v>0.5821167883211679</v>
       </c>
       <c r="AL4">
-        <v>2.58</v>
+        <v>1.41</v>
       </c>
       <c r="AM4">
-        <v>1.978</v>
+        <v>0.9969999999999999</v>
       </c>
       <c r="AN4">
-        <v>7.908285440613026</v>
+        <v>9.702770780856422</v>
       </c>
       <c r="AO4">
-        <v>12.09302325581395</v>
+        <v>27.3758865248227</v>
       </c>
       <c r="AP4">
-        <v>7.503122521744235</v>
+        <v>8.838790931989923</v>
       </c>
       <c r="AQ4">
-        <v>15.77350859453994</v>
+        <v>38.71614844533602</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Net Pacific Financial Holdings Limited (Catalist:5QY)</t>
+          <t>IFS Capital Limited (SGX:I49)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.327</v>
+        <v>0.0392</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1005,100 +1005,97 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.01208160967957599</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.01208160967957599</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.5669999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="L5">
-        <v>-1.4175</v>
+        <v>0.1731060606060606</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.11</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04386694386694386</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.461706783369803</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.04386694386694386</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.461706783369803</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>5.09</v>
+        <v>58.2</v>
       </c>
       <c r="V5">
-        <v>0.503960396039604</v>
+        <v>1.20997920997921</v>
       </c>
       <c r="W5">
-        <v>-0.04231343283582089</v>
+        <v>0.03520801232665639</v>
       </c>
       <c r="X5">
-        <v>0.02295363013095351</v>
+        <v>0.06643349732768751</v>
       </c>
       <c r="Y5">
-        <v>-0.0652670629667744</v>
+        <v>-0.03122548500103112</v>
       </c>
       <c r="Z5">
-        <v>0.04502052315373526</v>
+        <v>0.1011494252873563</v>
       </c>
       <c r="AA5">
-        <v>0.0005439203883137429</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02295420864330417</v>
+        <v>0.04734244663860092</v>
       </c>
       <c r="AC5">
-        <v>-0.02241028825499043</v>
+        <v>-0.04734244663860092</v>
       </c>
       <c r="AD5">
-        <v>0.017</v>
+        <v>113.6</v>
       </c>
       <c r="AE5">
-        <v>0.005836780640848019</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.02283678064084802</v>
+        <v>113.6</v>
       </c>
       <c r="AG5">
-        <v>-5.067163219359152</v>
+        <v>55.39999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.002255966497901223</v>
+        <v>0.7025355596784169</v>
       </c>
       <c r="AI5">
-        <v>0.00175359493676494</v>
+        <v>0.4446183953033268</v>
       </c>
       <c r="AJ5">
-        <v>-1.006820495123216</v>
+        <v>0.5352657004830917</v>
       </c>
       <c r="AK5">
-        <v>-0.6387580331571886</v>
+        <v>0.2807906741003547</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="AP5">
-        <v>-844.5272032265253</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hong Leong Finance Limited (SGX:S41)</t>
+          <t>Net Pacific Financial Holdings Limited (Catalist:5QY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,10 +1115,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00438</v>
-      </c>
-      <c r="E6">
-        <v>0.009010000000000001</v>
+        <v>-0.255</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1130,97 +1124,100 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.01092709941956441</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.01092709941956441</v>
       </c>
       <c r="K6">
-        <v>53.6</v>
+        <v>-0.575</v>
       </c>
       <c r="L6">
-        <v>0.4294871794871795</v>
+        <v>-1.292134831460674</v>
       </c>
       <c r="M6">
-        <v>63.2</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.07960700340093212</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>1.17910447761194</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>63.2</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07960700340093212</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>1.17910447761194</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>420.7</v>
+        <v>4.84</v>
       </c>
       <c r="V6">
-        <v>0.5299156064995592</v>
+        <v>0.5614849187935035</v>
       </c>
       <c r="W6">
-        <v>0.03920134571783808</v>
+        <v>-0.04423076923076923</v>
       </c>
       <c r="X6">
-        <v>0.0232691922758238</v>
+        <v>0.04813996605034442</v>
       </c>
       <c r="Y6">
-        <v>0.01593215344201428</v>
+        <v>-0.09237073528111364</v>
       </c>
       <c r="Z6">
-        <v>0.1644940621334142</v>
+        <v>0.05609700578982996</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.000612977559405352</v>
       </c>
       <c r="AB6">
-        <v>0.02308117462400067</v>
+        <v>0.0481383243325279</v>
       </c>
       <c r="AC6">
-        <v>-0.02308117462400067</v>
+        <v>-0.04752534677312256</v>
       </c>
       <c r="AD6">
-        <v>40.3</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.005687203791469195</v>
       </c>
       <c r="AF6">
-        <v>40.3</v>
+        <v>0.005687203791469195</v>
       </c>
       <c r="AG6">
-        <v>-380.4</v>
+        <v>-4.834312796208531</v>
       </c>
       <c r="AH6">
-        <v>0.04830975785183409</v>
+        <v>0.0006593334139185285</v>
       </c>
       <c r="AI6">
-        <v>0.02720032397408207</v>
+        <v>0.0004621606008087811</v>
       </c>
       <c r="AJ6">
-        <v>-0.9199516324062877</v>
+        <v>-1.276997421067128</v>
       </c>
       <c r="AK6">
-        <v>-0.3585634838344801</v>
+        <v>-0.6475375493569315</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>-805.7187993680884</v>
       </c>
     </row>
     <row r="7">
@@ -1240,10 +1237,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.106</v>
+        <v>0.0716</v>
       </c>
       <c r="E7">
-        <v>0.179</v>
+        <v>0.105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,28 +1255,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="L7">
-        <v>0.4955357142857143</v>
+        <v>0.5021276595744681</v>
       </c>
       <c r="M7">
-        <v>4.22</v>
+        <v>9.06</v>
       </c>
       <c r="N7">
-        <v>0.02463514302393461</v>
+        <v>0.05104225352112676</v>
       </c>
       <c r="O7">
-        <v>0.1900900900900901</v>
+        <v>0.3838983050847458</v>
       </c>
       <c r="P7">
-        <v>4.22</v>
+        <v>9.06</v>
       </c>
       <c r="Q7">
-        <v>0.02463514302393461</v>
+        <v>0.05104225352112676</v>
       </c>
       <c r="R7">
-        <v>0.1900900900900901</v>
+        <v>0.3838983050847458</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1288,55 +1285,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>235.1</v>
+        <v>133.6</v>
       </c>
       <c r="V7">
-        <v>1.372446001167542</v>
+        <v>0.7526760563380281</v>
       </c>
       <c r="W7">
-        <v>0.08225268618006669</v>
+        <v>0.08</v>
       </c>
       <c r="X7">
-        <v>0.02864380317337614</v>
+        <v>0.05327686004623222</v>
       </c>
       <c r="Y7">
-        <v>0.05360888300669055</v>
+        <v>0.02672313995376778</v>
       </c>
       <c r="Z7">
-        <v>0.535885167464115</v>
+        <v>0.2237029985721085</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.02431461887696809</v>
+        <v>0.04768490639419648</v>
       </c>
       <c r="AC7">
-        <v>-0.02431461887696809</v>
+        <v>-0.04768490639419648</v>
       </c>
       <c r="AD7">
-        <v>150.2</v>
+        <v>117.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>150.2</v>
+        <v>117.8</v>
       </c>
       <c r="AG7">
-        <v>-84.90000000000001</v>
+        <v>-15.8</v>
       </c>
       <c r="AH7">
-        <v>0.4671850699844479</v>
+        <v>0.3989163562478835</v>
       </c>
       <c r="AI7">
-        <v>0.3373764600179694</v>
+        <v>0.2918731417244796</v>
       </c>
       <c r="AJ7">
-        <v>-0.9826388888888888</v>
+        <v>-0.09771181199752628</v>
       </c>
       <c r="AK7">
-        <v>-0.4040932889100429</v>
+        <v>-0.05851851851851851</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1353,7 +1350,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IFS Capital Limited (SGX:I49)</t>
+          <t>Singapura Finance Ltd (SGX:S23)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1362,7 +1359,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.171</v>
+        <v>0.00312</v>
+      </c>
+      <c r="E8">
+        <v>0.09269999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.094</v>
+        <v>6.45</v>
       </c>
       <c r="L8">
-        <v>0.004051724137931034</v>
+        <v>0.3932926829268293</v>
       </c>
       <c r="M8">
-        <v>0.5590000000000001</v>
+        <v>4.56</v>
       </c>
       <c r="N8">
-        <v>0.01081237911025145</v>
+        <v>0.05038674033149171</v>
       </c>
       <c r="O8">
-        <v>5.946808510638299</v>
+        <v>0.7069767441860464</v>
       </c>
       <c r="P8">
-        <v>0.5590000000000001</v>
+        <v>4.56</v>
       </c>
       <c r="Q8">
-        <v>0.01081237911025145</v>
+        <v>0.05038674033149171</v>
       </c>
       <c r="R8">
-        <v>5.946808510638299</v>
+        <v>0.7069767441860464</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,55 +1407,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>38.4</v>
+        <v>47</v>
       </c>
       <c r="V8">
-        <v>0.7427466150870405</v>
+        <v>0.5193370165745856</v>
       </c>
       <c r="W8">
-        <v>0.0007315175097276264</v>
+        <v>0.03414505029115934</v>
       </c>
       <c r="X8">
-        <v>0.04428261220379582</v>
+        <v>0.04875040790734954</v>
       </c>
       <c r="Y8">
-        <v>-0.04355109469406819</v>
+        <v>-0.0146053576161902</v>
       </c>
       <c r="Z8">
-        <v>0.08929946112394149</v>
+        <v>0.1887226697353279</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.02519564682743508</v>
+        <v>0.04805183873083359</v>
       </c>
       <c r="AC8">
-        <v>-0.02519564682743508</v>
+        <v>-0.04805183873083359</v>
       </c>
       <c r="AD8">
-        <v>169.6</v>
+        <v>7.19</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>169.6</v>
+        <v>7.19</v>
       </c>
       <c r="AG8">
-        <v>131.2</v>
+        <v>-39.81</v>
       </c>
       <c r="AH8">
-        <v>0.7663804789877993</v>
+        <v>0.07360016378339647</v>
       </c>
       <c r="AI8">
-        <v>0.543415571932073</v>
+        <v>0.03920606358034789</v>
       </c>
       <c r="AJ8">
-        <v>0.7173318753417168</v>
+        <v>-0.7853620043401066</v>
       </c>
       <c r="AK8">
-        <v>0.4793569601753745</v>
+        <v>-0.2918835691766259</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eqonex Limited (NasdaqCM:EQOS)</t>
+          <t>Hong Leong Finance Limited (SGX:S41)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1480,113 +1480,235 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0413</v>
+      </c>
+      <c r="E9">
+        <v>0.0564</v>
+      </c>
       <c r="G9">
-        <v>-311.8466898954704</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-334.4947735191638</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-337.2822299651568</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-337.2822299651568</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-125.3</v>
+        <v>61.3</v>
       </c>
       <c r="L9">
-        <v>-436.5853658536586</v>
+        <v>0.4372325249643367</v>
       </c>
       <c r="M9">
+        <v>38.6</v>
+      </c>
+      <c r="N9">
+        <v>0.04832248372558839</v>
+      </c>
+      <c r="O9">
+        <v>0.6296900489396412</v>
+      </c>
+      <c r="P9">
+        <v>38.6</v>
+      </c>
+      <c r="Q9">
+        <v>0.04832248372558839</v>
+      </c>
+      <c r="R9">
+        <v>0.6296900489396412</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>435.3</v>
+      </c>
+      <c r="V9">
+        <v>0.5449424136204307</v>
+      </c>
+      <c r="W9">
+        <v>0.04253104835912024</v>
+      </c>
+      <c r="X9">
+        <v>0.04845687629790633</v>
+      </c>
+      <c r="Y9">
+        <v>-0.005925827938786099</v>
+      </c>
+      <c r="Z9">
+        <v>0.1321519464605524</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.04808984565717257</v>
+      </c>
+      <c r="AC9">
+        <v>-0.04808984565717257</v>
+      </c>
+      <c r="AD9">
+        <v>33.2</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>33.2</v>
+      </c>
+      <c r="AG9">
+        <v>-402.1</v>
+      </c>
+      <c r="AH9">
+        <v>0.03990384615384616</v>
+      </c>
+      <c r="AI9">
+        <v>0.02289181548645108</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.01361230148727</v>
+      </c>
+      <c r="AK9">
+        <v>-0.3961576354679804</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Eqonex Limited (OTCPK:EQOS.Q)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>-11.09056603773585</v>
+      </c>
+      <c r="H10">
+        <v>-12.64150943396226</v>
+      </c>
+      <c r="I10">
+        <v>-12.67924528301887</v>
+      </c>
+      <c r="J10">
+        <v>-12.67924528301887</v>
+      </c>
+      <c r="K10">
+        <v>-75</v>
+      </c>
+      <c r="L10">
+        <v>-14.15094339622642</v>
+      </c>
+      <c r="M10">
         <v>-0</v>
       </c>
-      <c r="N9">
+      <c r="N10">
         <v>-0</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>-0</v>
       </c>
-      <c r="Q9">
+      <c r="Q10">
         <v>-0</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>57.3</v>
-      </c>
-      <c r="V9">
-        <v>0.784931506849315</v>
-      </c>
-      <c r="W9">
-        <v>34.23497267759563</v>
-      </c>
-      <c r="X9">
-        <v>0.02309667450118563</v>
-      </c>
-      <c r="Y9">
-        <v>34.21187600309445</v>
-      </c>
-      <c r="Z9">
-        <v>0.0306951871657754</v>
-      </c>
-      <c r="AA9">
-        <v>-10.35294117647059</v>
-      </c>
-      <c r="AB9">
-        <v>0.02315922156369462</v>
-      </c>
-      <c r="AC9">
-        <v>-10.37610039803428</v>
-      </c>
-      <c r="AD9">
-        <v>1.77</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>1.77</v>
-      </c>
-      <c r="AG9">
-        <v>-55.52999999999999</v>
-      </c>
-      <c r="AH9">
-        <v>0.02367259596094691</v>
-      </c>
-      <c r="AI9">
-        <v>0.02815333227294417</v>
-      </c>
-      <c r="AJ9">
-        <v>-3.178591871780193</v>
-      </c>
-      <c r="AK9">
-        <v>-9.969479353680416</v>
-      </c>
-      <c r="AL9">
-        <v>1.04</v>
-      </c>
-      <c r="AM9">
-        <v>1.04</v>
-      </c>
-      <c r="AN9">
-        <v>-0.0184375</v>
-      </c>
-      <c r="AO9">
-        <v>-93.07692307692307</v>
-      </c>
-      <c r="AP9">
-        <v>0.5784374999999999</v>
-      </c>
-      <c r="AQ9">
-        <v>-93.07692307692307</v>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>6.4</v>
+      </c>
+      <c r="V10">
+        <v>5.039370078740157</v>
+      </c>
+      <c r="W10">
+        <v>-1.213592233009709</v>
+      </c>
+      <c r="X10">
+        <v>0.1006011450472279</v>
+      </c>
+      <c r="Y10">
+        <v>-1.314193378056937</v>
+      </c>
+      <c r="Z10">
+        <v>0.8452950558213712</v>
+      </c>
+      <c r="AA10">
+        <v>-10.71770334928229</v>
+      </c>
+      <c r="AB10">
+        <v>0.1246792760091164</v>
+      </c>
+      <c r="AC10">
+        <v>-10.84238262529141</v>
+      </c>
+      <c r="AD10">
+        <v>8.6</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>8.6</v>
+      </c>
+      <c r="AG10">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0.8713272543059778</v>
+      </c>
+      <c r="AI10">
+        <v>0.6771653543307087</v>
+      </c>
+      <c r="AJ10">
+        <v>0.6340057636887607</v>
+      </c>
+      <c r="AK10">
+        <v>0.3492063492063491</v>
+      </c>
+      <c r="AL10">
+        <v>0.271</v>
+      </c>
+      <c r="AM10">
+        <v>0.271</v>
+      </c>
+      <c r="AN10">
+        <v>-0.1283582089552239</v>
+      </c>
+      <c r="AO10">
+        <v>-247.970479704797</v>
+      </c>
+      <c r="AP10">
+        <v>-0.03283582089552238</v>
+      </c>
+      <c r="AQ10">
+        <v>-247.970479704797</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0392</v>
+        <v>0.0466</v>
       </c>
       <c r="E2">
-        <v>0.09269999999999999</v>
-      </c>
-      <c r="F2">
-        <v>0.05</v>
+        <v>0.0907</v>
       </c>
       <c r="G2">
-        <v>0.4010827426791831</v>
+        <v>0.4375291036817096</v>
       </c>
       <c r="H2">
-        <v>0.3055399795876381</v>
+        <v>0.3522527233177804</v>
       </c>
       <c r="I2">
-        <v>0.2896496920470386</v>
+        <v>0.3343887730229076</v>
       </c>
       <c r="J2">
-        <v>0.2505526980661979</v>
+        <v>0.2986804872431149</v>
       </c>
       <c r="K2">
-        <v>379.545</v>
+        <v>576.71</v>
       </c>
       <c r="L2">
-        <v>0.3062217363416691</v>
+        <v>0.4125194292781429</v>
       </c>
       <c r="M2">
-        <v>321.51</v>
+        <v>349.52</v>
       </c>
       <c r="N2">
-        <v>0.03806793761078135</v>
+        <v>0.03728977027828633</v>
       </c>
       <c r="O2">
-        <v>0.8470932300517725</v>
+        <v>0.6060585042742453</v>
       </c>
       <c r="P2">
-        <v>301.61</v>
+        <v>335.72</v>
       </c>
       <c r="Q2">
-        <v>0.03571170620754491</v>
+        <v>0.03581746875093353</v>
       </c>
       <c r="R2">
-        <v>0.7946620295353647</v>
+        <v>0.5821296665568484</v>
       </c>
       <c r="S2">
-        <v>19.89999999999998</v>
+        <v>13.80000000000001</v>
       </c>
       <c r="T2">
-        <v>0.06189543093527411</v>
+        <v>0.03948271915770202</v>
       </c>
       <c r="U2">
-        <v>1436.84</v>
+        <v>1787.416</v>
       </c>
       <c r="V2">
-        <v>0.1701270115289574</v>
+        <v>0.1906967613633939</v>
       </c>
       <c r="W2">
-        <v>0.03886953034288831</v>
+        <v>0.02711021764904385</v>
       </c>
       <c r="X2">
-        <v>0.05101378443741835</v>
+        <v>0.05042214239487699</v>
       </c>
       <c r="Y2">
-        <v>-0.01214425409453004</v>
+        <v>-0.02331192474583314</v>
       </c>
       <c r="Z2">
-        <v>0.5292470121719213</v>
+        <v>0.5238428223668331</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04805181993338715</v>
+        <v>0.04974880002140242</v>
       </c>
       <c r="AC2">
-        <v>-0.04760512658365952</v>
+        <v>-0.04968269656630432</v>
       </c>
       <c r="AD2">
-        <v>1232.59</v>
+        <v>1263.614</v>
       </c>
       <c r="AE2">
-        <v>0.005687203791469195</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AF2">
-        <v>1232.595687203791</v>
+        <v>1263.619709636439</v>
       </c>
       <c r="AG2">
-        <v>-204.2443127962088</v>
+        <v>-523.796290363561</v>
       </c>
       <c r="AH2">
-        <v>0.1273568198997758</v>
+        <v>0.1187980994228547</v>
       </c>
       <c r="AI2">
-        <v>0.265892278176543</v>
+        <v>0.2544229934525975</v>
       </c>
       <c r="AJ2">
-        <v>-0.0247825831229261</v>
+        <v>-0.05919081222282119</v>
       </c>
       <c r="AK2">
-        <v>-0.06384918007187264</v>
+        <v>-0.164757588937058</v>
       </c>
       <c r="AL2">
-        <v>6.991</v>
+        <v>15.949</v>
       </c>
       <c r="AM2">
-        <v>3.558</v>
+        <v>-5.944000000000001</v>
       </c>
       <c r="AN2">
-        <v>3.224092742462843</v>
+        <v>2.568237618288836</v>
       </c>
       <c r="AO2">
-        <v>51.3517379487913</v>
+        <v>29.31074048529689</v>
       </c>
       <c r="AP2">
-        <v>-0.534243022071871</v>
+        <v>-1.064591985552423</v>
       </c>
       <c r="AQ2">
-        <v>100.8993816750984</v>
+        <v>-78.64687079407805</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0654</v>
+        <v>0.0718</v>
       </c>
       <c r="E3">
-        <v>0.0585</v>
-      </c>
-      <c r="F3">
-        <v>0.05</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G3">
-        <v>0.6579746835443039</v>
+        <v>0.6546566961250849</v>
       </c>
       <c r="H3">
-        <v>0.5184810126582279</v>
+        <v>0.5203942895989123</v>
       </c>
       <c r="I3">
-        <v>0.4906329113924051</v>
+        <v>0.494108316338092</v>
       </c>
       <c r="J3">
-        <v>0.4071689218681799</v>
+        <v>0.4183893676805374</v>
       </c>
       <c r="K3">
-        <v>324.5</v>
+        <v>421.8</v>
       </c>
       <c r="L3">
-        <v>0.4107594936708861</v>
+        <v>0.477906186267845</v>
       </c>
       <c r="M3">
-        <v>265.9</v>
+        <v>268.1</v>
       </c>
       <c r="N3">
-        <v>0.03727587512091177</v>
+        <v>0.03363780080800984</v>
       </c>
       <c r="O3">
-        <v>0.8194144838212634</v>
+        <v>0.6356092935040304</v>
       </c>
       <c r="P3">
-        <v>246</v>
+        <v>254.3</v>
       </c>
       <c r="Q3">
-        <v>0.03448614245860962</v>
+        <v>0.03190635115806379</v>
       </c>
       <c r="R3">
-        <v>0.7580893682588598</v>
+        <v>0.6028923660502608</v>
       </c>
       <c r="S3">
-        <v>19.89999999999998</v>
+        <v>13.80000000000001</v>
       </c>
       <c r="T3">
-        <v>0.07484016547574268</v>
+        <v>0.05147333084669903</v>
       </c>
       <c r="U3">
-        <v>717.2</v>
+        <v>763.4</v>
       </c>
       <c r="V3">
-        <v>0.1005425258996537</v>
+        <v>0.09578178715716042</v>
       </c>
       <c r="W3">
-        <v>0.3151403321355735</v>
+        <v>0.3799657688496532</v>
       </c>
       <c r="X3">
-        <v>0.04875070882860448</v>
+        <v>0.05043371025600753</v>
       </c>
       <c r="Y3">
-        <v>0.266389623306969</v>
+        <v>0.3295320585936457</v>
       </c>
       <c r="Z3">
-        <v>3.291666666666668</v>
+        <v>1.957852706299912</v>
       </c>
       <c r="AA3">
-        <v>1.340264367816093</v>
+        <v>0.8191447558004491</v>
       </c>
       <c r="AB3">
-        <v>0.04805180113594073</v>
+        <v>0.04960950529978269</v>
       </c>
       <c r="AC3">
-        <v>1.292212566680152</v>
+        <v>0.7695352505006664</v>
       </c>
       <c r="AD3">
-        <v>567</v>
+        <v>537.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>567</v>
+        <v>537.4</v>
       </c>
       <c r="AG3">
-        <v>-150.2</v>
+        <v>-226</v>
       </c>
       <c r="AH3">
-        <v>0.07363349479890394</v>
+        <v>0.06316705063707743</v>
       </c>
       <c r="AI3">
-        <v>0.3373393622084722</v>
+        <v>0.2991871729206102</v>
       </c>
       <c r="AJ3">
-        <v>-0.0215090719021638</v>
+        <v>-0.02918313060096589</v>
       </c>
       <c r="AK3">
-        <v>-0.1558738065587381</v>
+        <v>-0.2188226181254841</v>
       </c>
       <c r="AL3">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="AM3">
-        <v>2.29</v>
+        <v>-15.44</v>
       </c>
       <c r="AN3">
-        <v>1.38427734375</v>
+        <v>1.170041367298062</v>
       </c>
       <c r="AO3">
-        <v>72.99435028248588</v>
+        <v>81.36194029850746</v>
       </c>
       <c r="AP3">
-        <v>-0.3666992187500001</v>
+        <v>-0.4920531243196168</v>
       </c>
       <c r="AQ3">
-        <v>169.2576419213974</v>
+        <v>-28.24481865284974</v>
       </c>
     </row>
     <row r="4">
@@ -862,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0392</v>
+        <v>0.0466</v>
       </c>
       <c r="E4">
-        <v>0.224</v>
+        <v>0.172</v>
       </c>
       <c r="G4">
-        <v>0.1689284043051006</v>
+        <v>0.1877667140825036</v>
       </c>
       <c r="H4">
-        <v>0.1689284043051006</v>
+        <v>0.1877667140825036</v>
       </c>
       <c r="I4">
-        <v>0.1806270472625176</v>
+        <v>0.1863442389758179</v>
       </c>
       <c r="J4">
-        <v>0.1542782959506795</v>
+        <v>0.157325746799431</v>
       </c>
       <c r="K4">
-        <v>34.7</v>
+        <v>32.7</v>
       </c>
       <c r="L4">
-        <v>0.1623771642489471</v>
+        <v>0.155049786628734</v>
       </c>
       <c r="M4">
-        <v>1.28</v>
+        <v>10.8</v>
       </c>
       <c r="N4">
-        <v>0.006823027718550107</v>
+        <v>0.05538461538461539</v>
       </c>
       <c r="O4">
-        <v>0.03688760806916426</v>
+        <v>0.3302752293577982</v>
       </c>
       <c r="P4">
-        <v>1.28</v>
+        <v>10.8</v>
       </c>
       <c r="Q4">
-        <v>0.006823027718550107</v>
+        <v>0.05538461538461539</v>
       </c>
       <c r="R4">
-        <v>0.03688760806916426</v>
+        <v>0.3302752293577982</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>34.3</v>
+        <v>7.91</v>
       </c>
       <c r="V4">
-        <v>0.1828358208955224</v>
+        <v>0.04056410256410257</v>
       </c>
       <c r="W4">
-        <v>0.1559550561797753</v>
+        <v>0.1316425120772947</v>
       </c>
       <c r="X4">
-        <v>0.06404371481419231</v>
+        <v>0.07404702558329052</v>
       </c>
       <c r="Y4">
-        <v>0.09191134136558297</v>
+        <v>0.05759548649400417</v>
       </c>
       <c r="Z4">
-        <v>0.4558447098976109</v>
+        <v>0.3519105623227098</v>
       </c>
       <c r="AA4">
-        <v>0.07032694506113524</v>
+        <v>0.05536459202402803</v>
       </c>
       <c r="AB4">
-        <v>0.04737634025688282</v>
+        <v>0.04743059717822348</v>
       </c>
       <c r="AC4">
-        <v>0.02295060480425242</v>
+        <v>0.007933994845804544</v>
       </c>
       <c r="AD4">
-        <v>385.2</v>
+        <v>516.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>385.2</v>
+        <v>516.7</v>
       </c>
       <c r="AG4">
-        <v>350.9</v>
+        <v>508.79</v>
       </c>
       <c r="AH4">
-        <v>0.6724860335195532</v>
+        <v>0.7260081495011943</v>
       </c>
       <c r="AI4">
-        <v>0.6046146601789357</v>
+        <v>0.6489575483546848</v>
       </c>
       <c r="AJ4">
-        <v>0.6516248839368616</v>
+        <v>0.7229287145313233</v>
       </c>
       <c r="AK4">
-        <v>0.5821167883211679</v>
+        <v>0.6454350556267364</v>
       </c>
       <c r="AL4">
-        <v>1.41</v>
+        <v>10.5</v>
       </c>
       <c r="AM4">
-        <v>0.9969999999999999</v>
+        <v>9.904</v>
       </c>
       <c r="AN4">
-        <v>9.702770780856422</v>
+        <v>12.75802469135803</v>
       </c>
       <c r="AO4">
-        <v>27.3758865248227</v>
+        <v>3.742857142857142</v>
       </c>
       <c r="AP4">
-        <v>8.838790931989923</v>
+        <v>12.56271604938272</v>
       </c>
       <c r="AQ4">
-        <v>38.71614844533602</v>
+        <v>3.968093699515347</v>
       </c>
     </row>
     <row r="5">
@@ -996,7 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0392</v>
+        <v>-0.0112</v>
+      </c>
+      <c r="E5">
+        <v>0.0867</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1011,28 +1008,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4.57</v>
+        <v>2.58</v>
       </c>
       <c r="L5">
-        <v>0.1731060606060606</v>
+        <v>0.0952029520295203</v>
       </c>
       <c r="M5">
-        <v>2.11</v>
+        <v>1.25</v>
       </c>
       <c r="N5">
-        <v>0.04386694386694386</v>
+        <v>0.03424657534246575</v>
       </c>
       <c r="O5">
-        <v>0.461706783369803</v>
+        <v>0.4844961240310077</v>
       </c>
       <c r="P5">
-        <v>2.11</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>0.04386694386694386</v>
+        <v>0.03424657534246575</v>
       </c>
       <c r="R5">
-        <v>0.461706783369803</v>
+        <v>0.4844961240310077</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1041,55 +1038,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>58.2</v>
+        <v>35</v>
       </c>
       <c r="V5">
-        <v>1.20997920997921</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="W5">
-        <v>0.03520801232665639</v>
+        <v>0.0205087440381558</v>
       </c>
       <c r="X5">
-        <v>0.06643349732768751</v>
+        <v>0.09275747131885193</v>
       </c>
       <c r="Y5">
-        <v>-0.03122548500103112</v>
+        <v>-0.07224872728069612</v>
       </c>
       <c r="Z5">
-        <v>0.1011494252873563</v>
+        <v>0.1495584988962473</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04734244663860092</v>
+        <v>0.04710704650860074</v>
       </c>
       <c r="AC5">
-        <v>-0.04734244663860092</v>
+        <v>-0.04710704650860074</v>
       </c>
       <c r="AD5">
-        <v>113.6</v>
+        <v>171.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>113.6</v>
+        <v>171.4</v>
       </c>
       <c r="AG5">
-        <v>55.39999999999999</v>
+        <v>136.4</v>
       </c>
       <c r="AH5">
-        <v>0.7025355596784169</v>
+        <v>0.8244348244348244</v>
       </c>
       <c r="AI5">
-        <v>0.4446183953033268</v>
+        <v>0.5408646260650047</v>
       </c>
       <c r="AJ5">
-        <v>0.5352657004830917</v>
+        <v>0.7888953152111047</v>
       </c>
       <c r="AK5">
-        <v>0.2807906741003547</v>
+        <v>0.4838595246541327</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1115,7 +1112,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.255</v>
+        <v>-0.168</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.01092709941956441</v>
+        <v>0.01081976105171503</v>
       </c>
       <c r="J6">
-        <v>0.01092709941956441</v>
+        <v>0.01081976105171503</v>
       </c>
       <c r="K6">
-        <v>-0.575</v>
+        <v>-0.355</v>
       </c>
       <c r="L6">
-        <v>-1.292134831460674</v>
+        <v>-0.7906458797327394</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1157,55 +1154,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.84</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>0.5614849187935035</v>
+        <v>0.8849557522123893</v>
       </c>
       <c r="W6">
-        <v>-0.04423076923076923</v>
+        <v>-0.02886178861788618</v>
       </c>
       <c r="X6">
-        <v>0.04813996605034442</v>
+        <v>0.04982485026273598</v>
       </c>
       <c r="Y6">
-        <v>-0.09237073528111364</v>
+        <v>-0.07868663888062215</v>
       </c>
       <c r="Z6">
-        <v>0.05609700578982996</v>
+        <v>0.06014163714705765</v>
       </c>
       <c r="AA6">
-        <v>0.000612977559405352</v>
+        <v>0.0006507181431901123</v>
       </c>
       <c r="AB6">
-        <v>0.0481383243325279</v>
+        <v>0.04981844267572751</v>
       </c>
       <c r="AC6">
-        <v>-0.04752534677312256</v>
+        <v>-0.0491677245325374</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0.005687203791469195</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AF6">
-        <v>0.005687203791469195</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AG6">
-        <v>-4.834312796208531</v>
+        <v>-5.994290363561101</v>
       </c>
       <c r="AH6">
-        <v>0.0006593334139185285</v>
+        <v>0.00084142068328997</v>
       </c>
       <c r="AI6">
-        <v>0.0004621606008087811</v>
+        <v>0.0004755767557104879</v>
       </c>
       <c r="AJ6">
-        <v>-1.276997421067128</v>
+        <v>-7.629141969963919</v>
       </c>
       <c r="AK6">
-        <v>-0.6475375493569315</v>
+        <v>-0.9980985972401141</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1217,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>-805.7187993680884</v>
+        <v>-999.0483939268501</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sing Investments &amp; Finance Limited (SGX:S35)</t>
+          <t>Singapura Finance Ltd (SGX:S23)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,10 +1234,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0716</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="E7">
-        <v>0.105</v>
+        <v>0.15</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1255,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>23.6</v>
+        <v>5.94</v>
       </c>
       <c r="L7">
-        <v>0.5021276595744681</v>
+        <v>0.3176470588235294</v>
       </c>
       <c r="M7">
-        <v>9.06</v>
+        <v>1.47</v>
       </c>
       <c r="N7">
-        <v>0.05104225352112676</v>
+        <v>0.01697459584295612</v>
       </c>
       <c r="O7">
-        <v>0.3838983050847458</v>
+        <v>0.2474747474747475</v>
       </c>
       <c r="P7">
-        <v>9.06</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>0.05104225352112676</v>
+        <v>0.01697459584295612</v>
       </c>
       <c r="R7">
-        <v>0.3838983050847458</v>
+        <v>0.2474747474747475</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,55 +1282,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>133.6</v>
+        <v>81.7</v>
       </c>
       <c r="V7">
-        <v>0.7526760563380281</v>
+        <v>0.943418013856813</v>
       </c>
       <c r="W7">
-        <v>0.08</v>
+        <v>0.0337116912599319</v>
       </c>
       <c r="X7">
-        <v>0.05327686004623222</v>
+        <v>0.05041057453374645</v>
       </c>
       <c r="Y7">
-        <v>0.02672313995376778</v>
+        <v>-0.01669888327381455</v>
       </c>
       <c r="Z7">
-        <v>0.2237029985721085</v>
+        <v>0.1371068260136374</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04768490639419648</v>
+        <v>0.04961682208222123</v>
       </c>
       <c r="AC7">
-        <v>-0.04768490639419648</v>
+        <v>-0.04961682208222123</v>
       </c>
       <c r="AD7">
-        <v>117.8</v>
+        <v>5.62</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>117.8</v>
+        <v>5.62</v>
       </c>
       <c r="AG7">
-        <v>-15.8</v>
+        <v>-76.08</v>
       </c>
       <c r="AH7">
-        <v>0.3989163562478835</v>
+        <v>0.06094122749945782</v>
       </c>
       <c r="AI7">
-        <v>0.2918731417244796</v>
+        <v>0.02937486932887309</v>
       </c>
       <c r="AJ7">
-        <v>-0.09771181199752628</v>
+        <v>-7.231939163498102</v>
       </c>
       <c r="AK7">
-        <v>-0.05851851851851851</v>
+        <v>-0.6940339354132458</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1350,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Singapura Finance Ltd (SGX:S23)</t>
+          <t>Hong Leong Finance Limited (SGX:S41)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1359,10 +1356,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.00312</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="E8">
-        <v>0.09269999999999999</v>
+        <v>0.0498</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,28 +1374,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>6.45</v>
+        <v>97.8</v>
       </c>
       <c r="L8">
-        <v>0.3932926829268293</v>
+        <v>0.5054263565891473</v>
       </c>
       <c r="M8">
-        <v>4.56</v>
+        <v>56.3</v>
       </c>
       <c r="N8">
-        <v>0.05038674033149171</v>
+        <v>0.06627427898763978</v>
       </c>
       <c r="O8">
-        <v>0.7069767441860464</v>
+        <v>0.5756646216768916</v>
       </c>
       <c r="P8">
-        <v>4.56</v>
+        <v>56.3</v>
       </c>
       <c r="Q8">
-        <v>0.05038674033149171</v>
+        <v>0.06627427898763978</v>
       </c>
       <c r="R8">
-        <v>0.7069767441860464</v>
+        <v>0.5756646216768916</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,55 +1404,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>47</v>
+        <v>547.3</v>
       </c>
       <c r="V8">
-        <v>0.5193370165745856</v>
+        <v>0.6442613301942318</v>
       </c>
       <c r="W8">
-        <v>0.03414505029115934</v>
+        <v>0.06901418389669042</v>
       </c>
       <c r="X8">
-        <v>0.04875040790734954</v>
+        <v>0.05001198264192597</v>
       </c>
       <c r="Y8">
-        <v>-0.0146053576161902</v>
+        <v>0.01900220125476446</v>
       </c>
       <c r="Z8">
-        <v>0.1887226697353279</v>
+        <v>0.19064039408867</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04805183873083359</v>
+        <v>0.0497485710503874</v>
       </c>
       <c r="AC8">
-        <v>-0.04805183873083359</v>
+        <v>-0.0497485710503874</v>
       </c>
       <c r="AD8">
-        <v>7.19</v>
+        <v>18.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>7.19</v>
+        <v>18.1</v>
       </c>
       <c r="AG8">
-        <v>-39.81</v>
+        <v>-529.1999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.07360016378339647</v>
+        <v>0.02086214845550945</v>
       </c>
       <c r="AI8">
-        <v>0.03920606358034789</v>
+        <v>0.01192987081465858</v>
       </c>
       <c r="AJ8">
-        <v>-0.7853620043401066</v>
+        <v>-1.652201061504839</v>
       </c>
       <c r="AK8">
-        <v>-0.2918835691766259</v>
+        <v>-0.5456232601299102</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1472,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hong Leong Finance Limited (SGX:S41)</t>
+          <t>Sing Investments &amp; Finance Limited (SGX:S35)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,10 +1478,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0413</v>
+        <v>0.0645</v>
       </c>
       <c r="E9">
-        <v>0.0564</v>
+        <v>0.0781</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,28 +1496,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>61.3</v>
+        <v>25.1</v>
       </c>
       <c r="L9">
-        <v>0.4372325249643367</v>
+        <v>0.4921568627450981</v>
       </c>
       <c r="M9">
-        <v>38.6</v>
+        <v>11.6</v>
       </c>
       <c r="N9">
-        <v>0.04832248372558839</v>
+        <v>0.06476828587381352</v>
       </c>
       <c r="O9">
-        <v>0.6296900489396412</v>
+        <v>0.4621513944223107</v>
       </c>
       <c r="P9">
-        <v>38.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q9">
-        <v>0.04832248372558839</v>
+        <v>0.06476828587381352</v>
       </c>
       <c r="R9">
-        <v>0.6296900489396412</v>
+        <v>0.4621513944223107</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1529,55 +1526,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>435.3</v>
+        <v>311.5</v>
       </c>
       <c r="V9">
-        <v>0.5449424136204307</v>
+        <v>1.739251814628699</v>
       </c>
       <c r="W9">
-        <v>0.04253104835912024</v>
+        <v>0.08782365290412876</v>
       </c>
       <c r="X9">
-        <v>0.04845687629790633</v>
+        <v>0.0500106540889069</v>
       </c>
       <c r="Y9">
-        <v>-0.005925827938786099</v>
+        <v>0.03781299881522186</v>
       </c>
       <c r="Z9">
-        <v>0.1321519464605524</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04808984565717257</v>
+        <v>0.04974902899241744</v>
       </c>
       <c r="AC9">
-        <v>-0.04808984565717257</v>
+        <v>-0.04974902899241744</v>
       </c>
       <c r="AD9">
-        <v>33.2</v>
+        <v>3.79</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>33.2</v>
+        <v>3.79</v>
       </c>
       <c r="AG9">
-        <v>-402.1</v>
+        <v>-307.71</v>
       </c>
       <c r="AH9">
-        <v>0.03990384615384616</v>
+        <v>0.02072283886489147</v>
       </c>
       <c r="AI9">
-        <v>0.02289181548645108</v>
+        <v>0.01221044492412771</v>
       </c>
       <c r="AJ9">
-        <v>-1.01361230148727</v>
+        <v>2.3925822253324</v>
       </c>
       <c r="AK9">
-        <v>-0.3961576354679804</v>
+        <v>277.216216216227</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1594,7 +1591,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eqonex Limited (OTCPK:EQOS.Q)</t>
+          <t>A-Smart Holdings Ltd. (SGX:BQC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1602,23 +1599,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.0258</v>
+      </c>
       <c r="G10">
-        <v>-11.09056603773585</v>
+        <v>-0.01467505241090147</v>
       </c>
       <c r="H10">
-        <v>-12.64150943396226</v>
+        <v>-0.01467505241090147</v>
       </c>
       <c r="I10">
-        <v>-12.67924528301887</v>
+        <v>-0.04884696016771489</v>
       </c>
       <c r="J10">
-        <v>-12.67924528301887</v>
+        <v>-0.04884696016771489</v>
       </c>
       <c r="K10">
-        <v>-75</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L10">
-        <v>-14.15094339622642</v>
+        <v>0.01781970649895178</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1627,7 +1627,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1636,79 +1636,314 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6.4</v>
+        <v>5.31</v>
       </c>
       <c r="V10">
-        <v>5.039370078740157</v>
+        <v>0.208235294117647</v>
       </c>
       <c r="W10">
-        <v>-1.213592233009709</v>
+        <v>0.00787037037037037</v>
       </c>
       <c r="X10">
-        <v>0.1006011450472279</v>
+        <v>0.05167109829433797</v>
       </c>
       <c r="Y10">
-        <v>-1.314193378056937</v>
+        <v>-0.0438007279239676</v>
       </c>
       <c r="Z10">
-        <v>0.8452950558213712</v>
+        <v>0.5533642691415313</v>
       </c>
       <c r="AA10">
-        <v>-10.71770334928229</v>
+        <v>-0.02703016241299304</v>
       </c>
       <c r="AB10">
-        <v>0.1246792760091164</v>
+        <v>0.0504496199186703</v>
       </c>
       <c r="AC10">
-        <v>-10.84238262529141</v>
+        <v>-0.07747978233166333</v>
       </c>
       <c r="AD10">
-        <v>8.6</v>
+        <v>5.17</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8.6</v>
+        <v>5.17</v>
       </c>
       <c r="AG10">
-        <v>2.199999999999999</v>
+        <v>-0.1399999999999997</v>
       </c>
       <c r="AH10">
-        <v>0.8713272543059778</v>
+        <v>0.1685686338441474</v>
       </c>
       <c r="AI10">
-        <v>0.6771653543307087</v>
+        <v>0.2550567340897879</v>
       </c>
       <c r="AJ10">
-        <v>0.6340057636887607</v>
+        <v>-0.005520504731861186</v>
       </c>
       <c r="AK10">
-        <v>0.3492063492063491</v>
+        <v>-0.009358288770053454</v>
       </c>
       <c r="AL10">
-        <v>0.271</v>
+        <v>0.03</v>
       </c>
       <c r="AM10">
-        <v>0.271</v>
+        <v>-0.075</v>
       </c>
       <c r="AN10">
-        <v>-0.1283582089552239</v>
+        <v>-73.85714285714285</v>
       </c>
       <c r="AO10">
-        <v>-247.970479704797</v>
+        <v>-7.766666666666667</v>
       </c>
       <c r="AP10">
-        <v>-0.03283582089552238</v>
+        <v>1.999999999999995</v>
       </c>
       <c r="AQ10">
-        <v>-247.970479704797</v>
+        <v>3.106666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OxPay Financial Limited (Catalist:TVV)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>-0.05498108448928121</v>
+      </c>
+      <c r="H11">
+        <v>-0.1026481715006305</v>
+      </c>
+      <c r="I11">
+        <v>-0.3152585119798235</v>
+      </c>
+      <c r="J11">
+        <v>-0.3152585119798235</v>
+      </c>
+      <c r="K11">
+        <v>-2.11</v>
+      </c>
+      <c r="L11">
+        <v>-0.266078184110971</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>28.5</v>
+      </c>
+      <c r="V11">
+        <v>2.28</v>
+      </c>
+      <c r="W11">
+        <v>-0.3669565217391304</v>
+      </c>
+      <c r="X11">
+        <v>0.05031020674340887</v>
+      </c>
+      <c r="Y11">
+        <v>-0.4172667284825393</v>
+      </c>
+      <c r="AB11">
+        <v>0.04989577109401935</v>
+      </c>
+      <c r="AD11">
+        <v>0.674</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.674</v>
+      </c>
+      <c r="AG11">
+        <v>-27.826</v>
+      </c>
+      <c r="AH11">
+        <v>0.05116137847274936</v>
+      </c>
+      <c r="AI11">
+        <v>0.1591875295229098</v>
+      </c>
+      <c r="AJ11">
+        <v>1.815607464439515</v>
+      </c>
+      <c r="AK11">
+        <v>1.146707327124372</v>
+      </c>
+      <c r="AL11">
+        <v>0.018</v>
+      </c>
+      <c r="AM11">
+        <v>-0.374</v>
+      </c>
+      <c r="AN11">
+        <v>-0.2653543307086614</v>
+      </c>
+      <c r="AO11">
+        <v>-138.8888888888889</v>
+      </c>
+      <c r="AP11">
+        <v>10.95511811023622</v>
+      </c>
+      <c r="AQ11">
+        <v>6.684491978609626</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OIO Holdings Limited (Catalist:KUX)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.404</v>
+      </c>
+      <c r="G12">
+        <v>-4.878504672897196</v>
+      </c>
+      <c r="H12">
+        <v>-5.19626168224299</v>
+      </c>
+      <c r="I12">
+        <v>-4.850467289719626</v>
+      </c>
+      <c r="J12">
+        <v>-4.850467289719626</v>
+      </c>
+      <c r="K12">
+        <v>-6.83</v>
+      </c>
+      <c r="L12">
+        <v>-6.383177570093458</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0.796</v>
+      </c>
+      <c r="V12">
+        <v>0.06982456140350878</v>
+      </c>
+      <c r="W12">
+        <v>-1.769430051813472</v>
+      </c>
+      <c r="X12">
+        <v>0.05363526847582126</v>
+      </c>
+      <c r="Y12">
+        <v>-1.823065320289293</v>
+      </c>
+      <c r="AB12">
+        <v>0.05272047115249767</v>
+      </c>
+      <c r="AD12">
+        <v>4.76</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>4.76</v>
+      </c>
+      <c r="AG12">
+        <v>3.964</v>
+      </c>
+      <c r="AH12">
+        <v>0.2945544554455445</v>
+      </c>
+      <c r="AI12">
+        <v>2.518518518518519</v>
+      </c>
+      <c r="AJ12">
+        <v>0.2580057276750846</v>
+      </c>
+      <c r="AK12">
+        <v>3.623400365630714</v>
+      </c>
+      <c r="AL12">
+        <v>0.041</v>
+      </c>
+      <c r="AM12">
+        <v>0.041</v>
+      </c>
+      <c r="AN12">
+        <v>-0.918918918918919</v>
+      </c>
+      <c r="AO12">
+        <v>-126.5853658536585</v>
+      </c>
+      <c r="AP12">
+        <v>-0.7652509652509653</v>
+      </c>
+      <c r="AQ12">
+        <v>-126.5853658536585</v>
       </c>
     </row>
   </sheetData>
